--- a/it_forms/043_user_agent_usage_audit_form--it_forms.xlsx
+++ b/it_forms/043_user_agent_usage_audit_form--it_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1098,7 +1098,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C67"/>
+  <dimension ref="A1:C62"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -1879,12 +1879,12 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>utc-5</t>
+          <t>utc+6</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>UTC-5</t>
+          <t>UTC+6</t>
         </is>
       </c>
     </row>
@@ -1896,12 +1896,12 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>utc+6</t>
+          <t>utc+3</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>UTC+6</t>
+          <t>UTC+3</t>
         </is>
       </c>
     </row>
@@ -1913,12 +1913,12 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>utc+3</t>
+          <t>utc-9</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>UTC+3</t>
+          <t>UTC-9</t>
         </is>
       </c>
     </row>
@@ -1930,12 +1930,12 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>utc-9</t>
+          <t>utc+4</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>UTC-9</t>
+          <t>UTC+4</t>
         </is>
       </c>
     </row>
@@ -1947,12 +1947,12 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>utc+4</t>
+          <t>utc-12</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>UTC+4</t>
+          <t>UTC-12</t>
         </is>
       </c>
     </row>
@@ -1964,97 +1964,97 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>utc-8</t>
+          <t>utc-1</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>UTC-8</t>
+          <t>UTC-1</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>geo_timezone_choices</t>
+          <t>geo_country_choices</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>utc-12</t>
+          <t>united_states</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>UTC-12</t>
+          <t>United States</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>geo_timezone_choices</t>
+          <t>geo_country_choices</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>utc-1</t>
+          <t>canada</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>UTC-1</t>
+          <t>Canada</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>geo_timezone_choices</t>
+          <t>geo_country_choices</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>utc+13</t>
+          <t>mexico</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>UTC+13</t>
+          <t>Mexico</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>geo_timezone_choices</t>
+          <t>geo_country_choices</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>utc-10</t>
+          <t>germany</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>UTC-10</t>
+          <t>Germany</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>geo_timezone_choices</t>
+          <t>geo_country_choices</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>utc-4</t>
+          <t>australia</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>UTC-4</t>
+          <t>Australia</t>
         </is>
       </c>
     </row>
@@ -2066,12 +2066,12 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>united_states</t>
+          <t>china</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>China</t>
         </is>
       </c>
     </row>
@@ -2083,12 +2083,12 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>canada</t>
+          <t>japan</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Canada</t>
+          <t>Japan</t>
         </is>
       </c>
     </row>
@@ -2100,12 +2100,12 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>mexico</t>
+          <t>south_korea</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Mexico</t>
+          <t>South Korea</t>
         </is>
       </c>
     </row>
@@ -2117,12 +2117,12 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>germany</t>
+          <t>india</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Germany</t>
+          <t>India</t>
         </is>
       </c>
     </row>
@@ -2134,12 +2134,12 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>australia</t>
+          <t>france</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Australia</t>
+          <t>France</t>
         </is>
       </c>
     </row>
@@ -2151,95 +2151,10 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>china</t>
+          <t>united_kingdom</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
-        <is>
-          <t>China</t>
-        </is>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63" t="inlineStr">
-        <is>
-          <t>geo_country_choices</t>
-        </is>
-      </c>
-      <c r="B63" t="inlineStr">
-        <is>
-          <t>japan</t>
-        </is>
-      </c>
-      <c r="C63" t="inlineStr">
-        <is>
-          <t>Japan</t>
-        </is>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" t="inlineStr">
-        <is>
-          <t>geo_country_choices</t>
-        </is>
-      </c>
-      <c r="B64" t="inlineStr">
-        <is>
-          <t>south_korea</t>
-        </is>
-      </c>
-      <c r="C64" t="inlineStr">
-        <is>
-          <t>South Korea</t>
-        </is>
-      </c>
-    </row>
-    <row r="65">
-      <c r="A65" t="inlineStr">
-        <is>
-          <t>geo_country_choices</t>
-        </is>
-      </c>
-      <c r="B65" t="inlineStr">
-        <is>
-          <t>india</t>
-        </is>
-      </c>
-      <c r="C65" t="inlineStr">
-        <is>
-          <t>India</t>
-        </is>
-      </c>
-    </row>
-    <row r="66">
-      <c r="A66" t="inlineStr">
-        <is>
-          <t>geo_country_choices</t>
-        </is>
-      </c>
-      <c r="B66" t="inlineStr">
-        <is>
-          <t>france</t>
-        </is>
-      </c>
-      <c r="C66" t="inlineStr">
-        <is>
-          <t>France</t>
-        </is>
-      </c>
-    </row>
-    <row r="67">
-      <c r="A67" t="inlineStr">
-        <is>
-          <t>geo_country_choices</t>
-        </is>
-      </c>
-      <c r="B67" t="inlineStr">
-        <is>
-          <t>united_kingdom</t>
-        </is>
-      </c>
-      <c r="C67" t="inlineStr">
         <is>
           <t>United Kingdom</t>
         </is>
